--- a/MR_UKBiobank/ContinuousData/gMR_res.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_res.xlsx
@@ -122,19 +122,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.931909497717575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7205324435091726</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.1432865519259776</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.10784543582061351</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.5645886360716805E-18</v>
+        <v>0.9024547199379768</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6988511058256401</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1060583340503134</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1038793949552738</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.704247082827798E-18</v>
       </c>
     </row>
   </sheetData>
@@ -176,19 +176,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.018562677370012253</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.018815966845103612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.055941321585128115</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01907073684444687</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3303748037030675</v>
+        <v>0.019042154019356005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.017140760913123696</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05522506895183571</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018460670883918215</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.30230711905110785</v>
       </c>
     </row>
   </sheetData>
@@ -230,19 +230,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08969700388260139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.05056345920535811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.12883054855984466</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01996609422308331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.0403087638715485E-6</v>
+        <v>0.08742346424326687</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.04954116689058179</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12530576159595194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019327702730961776</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.090568589478632E-6</v>
       </c>
     </row>
   </sheetData>
@@ -284,19 +284,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03574643494360698</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-9.362342688830558E-4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.07242910415609702</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.018715647557392873</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.056136322200357816</v>
+        <v>0.033451526838699897</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.0020579658081790048</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0689610194855788</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018117088085142296</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06483306289084438</v>
       </c>
     </row>
   </sheetData>
@@ -338,19 +338,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05915991830250599</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.017502068484797483</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.10081776812021451</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.021254005009034953</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.005378057859113937</v>
+        <v>0.055581311238197005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01348156164867359</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.09768106082772042</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021479464076287456</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.009663342525929413</v>
       </c>
     </row>
   </sheetData>
@@ -392,19 +392,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2237771824735491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.30798399463634796</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.13957037031075026</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0429626592667341</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.902260466411541E-7</v>
+        <v>-0.2133382117160196</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3012574055248699</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.12541901790716933</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04485673153512769</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.9747526195382063E-6</v>
       </c>
     </row>
   </sheetData>
@@ -446,19 +446,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2812374948697123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.20488944667524825</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.35758554306417634</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.038953085813502056</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.202473156067034E-13</v>
+        <v>0.2689825449182953</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.18641241173551004</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3515526781010806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.042127618970808814</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.7145868829752514E-10</v>
       </c>
     </row>
   </sheetData>
@@ -500,19 +500,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.15092675330312147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.22466237309051135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.0771911335157316</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.03762021417723973</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.024411777590431E-5</v>
+        <v>-0.14342688924425157</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.21885737412627332</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0679964043622298</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038484941266337634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.9390203610419114E-4</v>
       </c>
     </row>
   </sheetData>
@@ -554,19 +554,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.12179124549771227</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0712413738363865</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.17234111715903805</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.025790750847615188</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.3321091923976777E-6</v>
+        <v>0.11582840366459313</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.06324012506347912</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.16841668226570713</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02683075438832347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.581631714421938E-5</v>
       </c>
     </row>
   </sheetData>
@@ -608,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02943254833946728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.00789026014729145</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.066755356826226</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.019042249227938127</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.12219044078354165</v>
+        <v>0.028676763667937564</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.007452275193863964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0648058025297391</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01843318309275588</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.11977608157812868</v>
       </c>
     </row>
   </sheetData>
@@ -662,19 +662,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.020269808751112006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.06211246090909776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.021572843406873744</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.021348291917339668</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.342375764385139</v>
+        <v>-0.019859149202571848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.060364076719724775</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02064577831458108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.020665779345486187</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3365683416443059</v>
       </c>
     </row>
   </sheetData>

--- a/MR_UKBiobank/ContinuousData/gMR_res.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_res.xlsx
@@ -122,19 +122,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9024547199379768</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6988511058256401</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.1060583340503134</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1038793949552738</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.704247082827798E-18</v>
+        <v>0.931909497717575</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7205324435091726</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.1432865519259776</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.10784543582061351</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5645886360716805E-18</v>
       </c>
     </row>
   </sheetData>
@@ -176,19 +176,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.019042154019356005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.017140760913123696</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.05522506895183571</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.018460670883918215</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.30230711905110785</v>
+        <v>0.018562677370012253</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.018815966845103612</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.055941321585128115</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01907073684444687</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3303748037030675</v>
       </c>
     </row>
   </sheetData>
@@ -230,19 +230,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08742346424326687</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.04954116689058179</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.12530576159595194</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.019327702730961776</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.090568589478632E-6</v>
+        <v>0.08969700388260139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05056345920535811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.12883054855984466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01996609422308331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.0403087638715485E-6</v>
       </c>
     </row>
   </sheetData>
@@ -284,19 +284,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.033451526838699897</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.0020579658081790048</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0689610194855788</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.018117088085142296</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.06483306289084438</v>
+        <v>0.03574643494360698</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.362342688830558E-4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07242910415609702</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.018715647557392873</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.056136322200357816</v>
       </c>
     </row>
   </sheetData>
@@ -338,19 +338,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.055581311238197005</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.01348156164867359</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.09768106082772042</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.021479464076287456</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.009663342525929413</v>
+        <v>0.05915991830250599</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.017502068484797483</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.10081776812021451</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021254005009034953</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005378057859113937</v>
       </c>
     </row>
   </sheetData>
@@ -392,19 +392,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2133382117160196</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.3012574055248699</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.12541901790716933</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.04485673153512769</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.9747526195382063E-6</v>
+        <v>-0.2237771824735491</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.30798399463634796</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13957037031075026</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0429626592667341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.902260466411541E-7</v>
       </c>
     </row>
   </sheetData>
@@ -446,19 +446,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2689825449182953</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.18641241173551004</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3515526781010806</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.042127618970808814</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.7145868829752514E-10</v>
+        <v>0.2812374948697123</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20488944667524825</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.35758554306417634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.038953085813502056</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.202473156067034E-13</v>
       </c>
     </row>
   </sheetData>
@@ -500,19 +500,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.14342688924425157</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.21885737412627332</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.0679964043622298</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.038484941266337634</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.9390203610419114E-4</v>
+        <v>-0.15092675330312147</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.22466237309051135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0771911335157316</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03762021417723973</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.024411777590431E-5</v>
       </c>
     </row>
   </sheetData>
@@ -554,19 +554,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.11582840366459313</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.06324012506347912</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.16841668226570713</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.02683075438832347</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.581631714421938E-5</v>
+        <v>0.12179124549771227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0712413738363865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.17234111715903805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.025790750847615188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.3321091923976777E-6</v>
       </c>
     </row>
   </sheetData>
@@ -608,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.028676763667937564</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.007452275193863964</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.0648058025297391</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01843318309275588</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.11977608157812868</v>
+        <v>0.02943254833946728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.00789026014729145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.066755356826226</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019042249227938127</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.12219044078354165</v>
       </c>
     </row>
   </sheetData>
@@ -662,19 +662,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.019859149202571848</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.060364076719724775</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.02064577831458108</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.020665779345486187</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3365683416443059</v>
+        <v>-0.020269808751112006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06211246090909776</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.021572843406873744</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.021348291917339668</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.342375764385139</v>
       </c>
     </row>
   </sheetData>

--- a/MR_UKBiobank/ContinuousData/gMR_res.xlsx
+++ b/MR_UKBiobank/ContinuousData/gMR_res.xlsx
@@ -122,19 +122,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.931909497717575</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7205324435091726</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.1432865519259776</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.10784543582061351</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.5645886360716805E-18</v>
+        <v>0.8536189101954307</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6693768660490713</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.03786095434179</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09400104293181599</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.076297951935484E-19</v>
       </c>
     </row>
   </sheetData>
@@ -176,19 +176,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.018562677370012253</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.018815966845103612</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.055941321585128115</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01907073684444687</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3303748037030675</v>
+        <v>-0.033283303946699976</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.07925380345629918</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.012687195562899219</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.023454336484489385</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.15587912281907187</v>
       </c>
     </row>
   </sheetData>
@@ -230,19 +230,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08969700388260139</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.05056345920535811</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.12883054855984466</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01996609422308331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.0403087638715485E-6</v>
+        <v>0.09985600461582508</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.05180849243640198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.14790351679524819</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.024514036826236277</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.632747140070241E-5</v>
       </c>
     </row>
   </sheetData>
@@ -284,19 +284,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03574643494360698</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-9.362342688830558E-4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.07242910415609702</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.018715647557392873</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.056136322200357816</v>
+        <v>0.04338228883560052</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.0018567118249717754</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.08862128949617282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.023081122786006273</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0601684609218871</v>
       </c>
     </row>
   </sheetData>
@@ -338,19 +338,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05915991830250599</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.017502068484797483</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.10081776812021451</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.021254005009034953</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.005378057859113937</v>
+        <v>0.07935919124123612</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.033520426325805645</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1251979561566666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.023387124956852287</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.905962873729093E-4</v>
       </c>
     </row>
   </sheetData>
@@ -392,19 +392,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2237771824735491</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.30798399463634796</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.13957037031075026</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0429626592667341</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.902260466411541E-7</v>
+        <v>-0.20405395489588937</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2699551781058465</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13815273168593223</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03362307306630467</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.2881585287261186E-9</v>
       </c>
     </row>
   </sheetData>
@@ -446,19 +446,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2812374948697123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.20488944667524825</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.35758554306417634</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.038953085813502056</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.202473156067034E-13</v>
+        <v>0.3005357360470901</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.22989008276586548</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.37118138932831474</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03604370065368604</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.549804666958009E-17</v>
       </c>
     </row>
   </sheetData>
@@ -500,19 +500,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.15092675330312147</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.22466237309051135</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.0771911335157316</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.03762021417723973</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.024411777590431E-5</v>
+        <v>-0.1551947792111054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2180211168533524</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.09236844156885839</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.032054253899105614</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.287795581618416E-6</v>
       </c>
     </row>
   </sheetData>
@@ -554,19 +554,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.12179124549771227</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0712413738363865</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.17234111715903805</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.025790750847615188</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.3321091923976777E-6</v>
+        <v>0.14019795932791168</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09126120765151263</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.18913471100431073</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.024967730447142376</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.9637325502070647E-8</v>
       </c>
     </row>
   </sheetData>
@@ -608,19 +608,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02943254833946728</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.00789026014729145</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.066755356826226</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.019042249227938127</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.12219044078354165</v>
+        <v>0.03418569379912404</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.011857863520309285</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.08022925111855736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0234916108772619</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1456056347013055</v>
       </c>
     </row>
   </sheetData>
@@ -662,19 +662,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.020269808751112006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.06211246090909776</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.021572843406873744</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.021348291917339668</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.342375764385139</v>
+        <v>-0.08612805453471288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.14515213552735096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.027103973542074805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.030114327037060244</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.004235931370790505</v>
       </c>
     </row>
   </sheetData>
